--- a/Sample Templates/Shikshalokam/Prod_ Shikshalokam Observation with rubrics.xlsx
+++ b/Sample Templates/Shikshalokam/Prod_ Shikshalokam Observation with rubrics.xlsx
@@ -5,20 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="details" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="framework" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ECMs or Domains" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="questions" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Criteria_Rubric-Scoring" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Domain(theme)_rubric_scoring" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="details" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="framework" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="ECMs or Domains" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="questions" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Criteria_Rubric-Scoring" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Domain(theme)_rubric_scoring" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="4" name="Z_D4A87F07_6279_4DF8_802E_5C9924B757F6_.wvu.FilterData" vbProcedure="false">questions!$A$2:$CG$6</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="Z_E12E26CB_2594_4F2A_B83D_1BA7E4E1D288_.wvu.FilterData" vbProcedure="false">questions!$A$2:$CG$6</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="Z_D4A87F07_6279_4DF8_802E_5C9924B757F6_.wvu.FilterData" vbProcedure="false">questions!$A$2:$CG$6</definedName>
+    <definedName function="false" hidden="false" localSheetId="4" name="Z_E12E26CB_2594_4F2A_B83D_1BA7E4E1D288_.wvu.FilterData" vbProcedure="false">questions!$A$2:$CG$6</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -700,6 +700,7 @@
         <color rgb="FF980000"/>
         <rFont val="Noto Sans Devanagari"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ಶಾಲೆಯಲ್ಲಿ ಪುಸ್ತಕಗಳ ಸಂಖ್ಯೆ ಇಲ್ಲವೇ</t>
     </r>
@@ -1114,12 +1115,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="@"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1144,7 +1146,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1152,7 +1154,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1189,13 +1191,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1214,7 +1209,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1227,36 +1222,24 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF980000"/>
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans Devanagari"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="8"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1401,7 +1384,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1518,19 +1501,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1542,23 +1517,23 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1566,15 +1541,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1582,11 +1553,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1594,7 +1565,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1626,12 +1597,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1646,20 +1613,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1670,11 +1629,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1682,15 +1641,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1698,7 +1657,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1778,186 +1737,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
-  <a:themeElements>
-    <a:clrScheme name="Sheets">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4f81bd"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="c0504d"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9bbb59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064a2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4bacc6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="f79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ff"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="0000ff"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Sheets">
-      <a:majorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="43.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70"/>
@@ -30321,12 +30107,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="41.43"/>
@@ -30334,7 +30120,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="18.43"/>
   </cols>
@@ -30410,13 +30196,13 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
         <v>154</v>
       </c>
       <c r="D3" s="14" t="s">
@@ -30425,19 +30211,19 @@
       <c r="E3" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="F3" s="32" t="b">
+      <c r="F3" s="30" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="31" t="s">
         <v>157</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -30473,12 +30259,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="39.43"/>
@@ -30490,96 +30276,96 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
       <c r="H1" s="22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -30596,12 +30382,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55.29"/>
@@ -30628,54 +30414,54 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="41" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="42" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="E3" s="48" t="b">
+      <c r="E3" s="45" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="48" t="b">
+      <c r="E4" s="45" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -30698,19 +30484,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:CG6"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="57.71"/>
@@ -30809,65 +30595,65 @@
       <c r="AA1" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="AB1" s="49" t="s">
+      <c r="AB1" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="AC1" s="49"/>
-      <c r="AD1" s="49"/>
-      <c r="AE1" s="49"/>
-      <c r="AF1" s="49"/>
-      <c r="AG1" s="49"/>
-      <c r="AH1" s="49"/>
-      <c r="AI1" s="49"/>
-      <c r="AJ1" s="49"/>
-      <c r="AK1" s="49"/>
-      <c r="AL1" s="49"/>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="49"/>
-      <c r="AP1" s="49"/>
-      <c r="AQ1" s="49"/>
-      <c r="AR1" s="49"/>
-      <c r="AS1" s="49"/>
-      <c r="AT1" s="49"/>
-      <c r="AU1" s="49"/>
-      <c r="AV1" s="49"/>
-      <c r="AW1" s="49"/>
-      <c r="AX1" s="49"/>
-      <c r="AY1" s="49"/>
-      <c r="AZ1" s="49"/>
-      <c r="BA1" s="49"/>
-      <c r="BB1" s="49"/>
-      <c r="BC1" s="49"/>
-      <c r="BD1" s="49"/>
-      <c r="BE1" s="49"/>
-      <c r="BF1" s="49"/>
-      <c r="BG1" s="49"/>
-      <c r="BH1" s="49"/>
-      <c r="BI1" s="49"/>
-      <c r="BJ1" s="49"/>
-      <c r="BK1" s="49"/>
-      <c r="BL1" s="49"/>
-      <c r="BM1" s="49"/>
-      <c r="BN1" s="49"/>
-      <c r="BO1" s="49"/>
-      <c r="BP1" s="49"/>
-      <c r="BQ1" s="49"/>
-      <c r="BR1" s="49"/>
-      <c r="BS1" s="49"/>
-      <c r="BT1" s="49"/>
-      <c r="BU1" s="49"/>
-      <c r="BV1" s="49"/>
-      <c r="BW1" s="49"/>
-      <c r="BX1" s="49"/>
-      <c r="BY1" s="49"/>
-      <c r="BZ1" s="49"/>
-      <c r="CA1" s="49"/>
-      <c r="CB1" s="49"/>
-      <c r="CC1" s="49"/>
-      <c r="CD1" s="49"/>
-      <c r="CE1" s="49"/>
-      <c r="CF1" s="49"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
+      <c r="AV1" s="46"/>
+      <c r="AW1" s="46"/>
+      <c r="AX1" s="46"/>
+      <c r="AY1" s="46"/>
+      <c r="AZ1" s="46"/>
+      <c r="BA1" s="46"/>
+      <c r="BB1" s="46"/>
+      <c r="BC1" s="46"/>
+      <c r="BD1" s="46"/>
+      <c r="BE1" s="46"/>
+      <c r="BF1" s="46"/>
+      <c r="BG1" s="46"/>
+      <c r="BH1" s="46"/>
+      <c r="BI1" s="46"/>
+      <c r="BJ1" s="46"/>
+      <c r="BK1" s="46"/>
+      <c r="BL1" s="46"/>
+      <c r="BM1" s="46"/>
+      <c r="BN1" s="46"/>
+      <c r="BO1" s="46"/>
+      <c r="BP1" s="46"/>
+      <c r="BQ1" s="46"/>
+      <c r="BR1" s="46"/>
+      <c r="BS1" s="46"/>
+      <c r="BT1" s="46"/>
+      <c r="BU1" s="46"/>
+      <c r="BV1" s="46"/>
+      <c r="BW1" s="46"/>
+      <c r="BX1" s="46"/>
+      <c r="BY1" s="46"/>
+      <c r="BZ1" s="46"/>
+      <c r="CA1" s="46"/>
+      <c r="CB1" s="46"/>
+      <c r="CC1" s="46"/>
+      <c r="CD1" s="46"/>
+      <c r="CE1" s="46"/>
+      <c r="CF1" s="46"/>
       <c r="CG1" s="22" t="s">
         <v>210</v>
       </c>
@@ -30879,7 +30665,7 @@
       <c r="B2" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="47" t="s">
         <v>50</v>
       </c>
       <c r="D2" s="27" t="s">
@@ -30888,364 +30674,364 @@
       <c r="E2" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="47" t="s">
         <v>77</v>
       </c>
       <c r="L2" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="48" t="s">
         <v>93</v>
       </c>
       <c r="Q2" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="48" t="s">
         <v>100</v>
       </c>
       <c r="S2" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="V2" s="50" t="s">
+      <c r="V2" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="W2" s="50" t="s">
+      <c r="W2" s="47" t="s">
         <v>117</v>
       </c>
       <c r="X2" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="Y2" s="51" t="s">
+      <c r="Y2" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="Z2" s="51" t="s">
+      <c r="Z2" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="AA2" s="50" t="s">
+      <c r="AA2" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="AB2" s="51" t="s">
+      <c r="AB2" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="AC2" s="51" t="s">
+      <c r="AC2" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="AD2" s="50" t="s">
+      <c r="AD2" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="AE2" s="51" t="s">
+      <c r="AE2" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="AF2" s="51" t="s">
+      <c r="AF2" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="AG2" s="50" t="s">
+      <c r="AG2" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="AH2" s="51" t="s">
+      <c r="AH2" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="AI2" s="51" t="s">
+      <c r="AI2" s="48" t="s">
         <v>218</v>
       </c>
-      <c r="AJ2" s="50" t="s">
+      <c r="AJ2" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="AK2" s="51" t="s">
+      <c r="AK2" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="AL2" s="51" t="s">
+      <c r="AL2" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="AM2" s="50" t="s">
+      <c r="AM2" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="AN2" s="51" t="s">
+      <c r="AN2" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="AO2" s="51" t="s">
+      <c r="AO2" s="48" t="s">
         <v>224</v>
       </c>
-      <c r="AP2" s="50" t="s">
+      <c r="AP2" s="47" t="s">
         <v>225</v>
       </c>
-      <c r="AQ2" s="51" t="s">
+      <c r="AQ2" s="48" t="s">
         <v>226</v>
       </c>
-      <c r="AR2" s="51" t="s">
+      <c r="AR2" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="AS2" s="50" t="s">
+      <c r="AS2" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="AT2" s="51" t="s">
+      <c r="AT2" s="48" t="s">
         <v>229</v>
       </c>
-      <c r="AU2" s="51" t="s">
+      <c r="AU2" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="AV2" s="50" t="s">
+      <c r="AV2" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="AW2" s="51" t="s">
+      <c r="AW2" s="48" t="s">
         <v>232</v>
       </c>
-      <c r="AX2" s="51" t="s">
+      <c r="AX2" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="AY2" s="50" t="s">
+      <c r="AY2" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="AZ2" s="51" t="s">
+      <c r="AZ2" s="48" t="s">
         <v>235</v>
       </c>
-      <c r="BA2" s="51" t="s">
+      <c r="BA2" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="BB2" s="50" t="s">
+      <c r="BB2" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="BC2" s="51" t="s">
+      <c r="BC2" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="BD2" s="51" t="s">
+      <c r="BD2" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="BE2" s="50" t="s">
+      <c r="BE2" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="BF2" s="51" t="s">
+      <c r="BF2" s="48" t="s">
         <v>241</v>
       </c>
-      <c r="BG2" s="51" t="s">
+      <c r="BG2" s="48" t="s">
         <v>242</v>
       </c>
-      <c r="BH2" s="50" t="s">
+      <c r="BH2" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="BI2" s="51" t="s">
+      <c r="BI2" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="BJ2" s="51" t="s">
+      <c r="BJ2" s="48" t="s">
         <v>245</v>
       </c>
-      <c r="BK2" s="50" t="s">
+      <c r="BK2" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="BL2" s="51" t="s">
+      <c r="BL2" s="48" t="s">
         <v>247</v>
       </c>
-      <c r="BM2" s="51" t="s">
+      <c r="BM2" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="BN2" s="50" t="s">
+      <c r="BN2" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="BO2" s="51" t="s">
+      <c r="BO2" s="48" t="s">
         <v>250</v>
       </c>
-      <c r="BP2" s="51" t="s">
+      <c r="BP2" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="BQ2" s="50" t="s">
+      <c r="BQ2" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="BR2" s="51" t="s">
+      <c r="BR2" s="48" t="s">
         <v>253</v>
       </c>
-      <c r="BS2" s="51" t="s">
+      <c r="BS2" s="48" t="s">
         <v>254</v>
       </c>
-      <c r="BT2" s="50" t="s">
+      <c r="BT2" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="BU2" s="51" t="s">
+      <c r="BU2" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="BV2" s="51" t="s">
+      <c r="BV2" s="48" t="s">
         <v>257</v>
       </c>
-      <c r="BW2" s="50" t="s">
+      <c r="BW2" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="BX2" s="51" t="s">
+      <c r="BX2" s="48" t="s">
         <v>259</v>
       </c>
-      <c r="BY2" s="51" t="s">
+      <c r="BY2" s="48" t="s">
         <v>260</v>
       </c>
-      <c r="BZ2" s="50" t="s">
+      <c r="BZ2" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="CA2" s="51" t="s">
+      <c r="CA2" s="48" t="s">
         <v>262</v>
       </c>
-      <c r="CB2" s="51" t="s">
+      <c r="CB2" s="48" t="s">
         <v>263</v>
       </c>
-      <c r="CC2" s="50" t="s">
+      <c r="CC2" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="CD2" s="51" t="s">
+      <c r="CD2" s="48" t="s">
         <v>265</v>
       </c>
-      <c r="CE2" s="51" t="s">
+      <c r="CE2" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="CF2" s="50" t="s">
+      <c r="CF2" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="CG2" s="50" t="s">
+      <c r="CG2" s="47" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="49" t="s">
         <v>268</v>
       </c>
-      <c r="E3" s="53" t="n">
+      <c r="E3" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="52" t="s">
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="49" t="s">
         <v>269</v>
       </c>
-      <c r="K3" s="53" t="n">
+      <c r="K3" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="M3" s="56" t="s">
+      <c r="M3" s="53" t="s">
         <v>271</v>
       </c>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="54"/>
-      <c r="Q3" s="52" t="s">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="49" t="s">
         <v>272</v>
       </c>
-      <c r="R3" s="57"/>
-      <c r="S3" s="58" t="b">
+      <c r="R3" s="54"/>
+      <c r="S3" s="54" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="T3" s="54"/>
-      <c r="U3" s="54"/>
-      <c r="V3" s="58" t="b">
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="54" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W3" s="58" t="b">
+      <c r="W3" s="54" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X3" s="53" t="n">
+      <c r="X3" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="54"/>
-      <c r="AC3" s="54"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="54"/>
-      <c r="AH3" s="54"/>
-      <c r="AI3" s="54"/>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="54"/>
-      <c r="AP3" s="54"/>
-      <c r="AQ3" s="54"/>
-      <c r="AR3" s="54"/>
-      <c r="AS3" s="54"/>
-      <c r="AT3" s="54"/>
-      <c r="AU3" s="54"/>
-      <c r="AV3" s="54"/>
-      <c r="AW3" s="54"/>
-      <c r="AX3" s="54"/>
-      <c r="AY3" s="54"/>
-      <c r="AZ3" s="54"/>
-      <c r="BA3" s="54"/>
-      <c r="BB3" s="54"/>
-      <c r="BC3" s="54"/>
-      <c r="BD3" s="54"/>
-      <c r="BE3" s="54"/>
-      <c r="BF3" s="54"/>
-      <c r="BG3" s="54"/>
-      <c r="BH3" s="54"/>
-      <c r="BI3" s="54"/>
-      <c r="BJ3" s="54"/>
-      <c r="BK3" s="54"/>
-      <c r="BL3" s="54"/>
-      <c r="BM3" s="54"/>
-      <c r="BN3" s="54"/>
-      <c r="BO3" s="54"/>
-      <c r="BP3" s="54"/>
-      <c r="BQ3" s="54"/>
-      <c r="BR3" s="54"/>
-      <c r="BS3" s="54"/>
-      <c r="BT3" s="54"/>
-      <c r="BU3" s="54"/>
-      <c r="BV3" s="54"/>
-      <c r="BW3" s="54"/>
-      <c r="BX3" s="54"/>
-      <c r="BY3" s="54"/>
-      <c r="BZ3" s="54"/>
-      <c r="CA3" s="54"/>
-      <c r="CB3" s="54"/>
-      <c r="CC3" s="54"/>
-      <c r="CD3" s="54"/>
-      <c r="CE3" s="54"/>
-      <c r="CF3" s="54"/>
-      <c r="CG3" s="54"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="51"/>
+      <c r="AE3" s="51"/>
+      <c r="AF3" s="51"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
+      <c r="AL3" s="51"/>
+      <c r="AM3" s="51"/>
+      <c r="AN3" s="51"/>
+      <c r="AO3" s="51"/>
+      <c r="AP3" s="51"/>
+      <c r="AQ3" s="51"/>
+      <c r="AR3" s="51"/>
+      <c r="AS3" s="51"/>
+      <c r="AT3" s="51"/>
+      <c r="AU3" s="51"/>
+      <c r="AV3" s="51"/>
+      <c r="AW3" s="51"/>
+      <c r="AX3" s="51"/>
+      <c r="AY3" s="51"/>
+      <c r="AZ3" s="51"/>
+      <c r="BA3" s="51"/>
+      <c r="BB3" s="51"/>
+      <c r="BC3" s="51"/>
+      <c r="BD3" s="51"/>
+      <c r="BE3" s="51"/>
+      <c r="BF3" s="51"/>
+      <c r="BG3" s="51"/>
+      <c r="BH3" s="51"/>
+      <c r="BI3" s="51"/>
+      <c r="BJ3" s="51"/>
+      <c r="BK3" s="51"/>
+      <c r="BL3" s="51"/>
+      <c r="BM3" s="51"/>
+      <c r="BN3" s="51"/>
+      <c r="BO3" s="51"/>
+      <c r="BP3" s="51"/>
+      <c r="BQ3" s="51"/>
+      <c r="BR3" s="51"/>
+      <c r="BS3" s="51"/>
+      <c r="BT3" s="51"/>
+      <c r="BU3" s="51"/>
+      <c r="BV3" s="51"/>
+      <c r="BW3" s="51"/>
+      <c r="BX3" s="51"/>
+      <c r="BY3" s="51"/>
+      <c r="BZ3" s="51"/>
+      <c r="CA3" s="51"/>
+      <c r="CB3" s="51"/>
+      <c r="CC3" s="51"/>
+      <c r="CD3" s="51"/>
+      <c r="CE3" s="51"/>
+      <c r="CF3" s="51"/>
+      <c r="CG3" s="51"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
@@ -31260,7 +31046,7 @@
       <c r="D4" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="E4" s="59" t="n">
+      <c r="E4" s="55" t="n">
         <v>2</v>
       </c>
       <c r="F4" s="14"/>
@@ -31270,13 +31056,13 @@
       <c r="J4" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K4" s="59" t="n">
+      <c r="K4" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="60" t="s">
+      <c r="L4" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="M4" s="61" t="s">
+      <c r="M4" s="57" t="s">
         <v>275</v>
       </c>
       <c r="N4" s="14"/>
@@ -31287,42 +31073,42 @@
       <c r="Q4" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="R4" s="62"/>
-      <c r="S4" s="63" t="b">
+      <c r="R4" s="58"/>
+      <c r="S4" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="T4" s="14"/>
       <c r="U4" s="14"/>
-      <c r="V4" s="63" t="b">
+      <c r="V4" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W4" s="63" t="b">
+      <c r="W4" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X4" s="59" t="n">
+      <c r="X4" s="55" t="n">
         <v>1</v>
       </c>
       <c r="Y4" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="Z4" s="59" t="n">
+      <c r="Z4" s="55" t="n">
         <v>20</v>
       </c>
       <c r="AA4" s="14"/>
       <c r="AB4" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="AC4" s="59" t="n">
+      <c r="AC4" s="55" t="n">
         <v>40</v>
       </c>
       <c r="AD4" s="14"/>
-      <c r="AE4" s="64" t="s">
+      <c r="AE4" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="AF4" s="59" t="n">
+      <c r="AF4" s="55" t="n">
         <v>60</v>
       </c>
       <c r="AG4" s="14"/>
@@ -31392,7 +31178,7 @@
       <c r="D5" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="59" t="n">
+      <c r="E5" s="55" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="10" t="s">
@@ -31408,13 +31194,13 @@
       <c r="J5" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="K5" s="59" t="n">
+      <c r="K5" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="65" t="s">
+      <c r="L5" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="M5" s="61" t="s">
+      <c r="M5" s="57" t="s">
         <v>285</v>
       </c>
       <c r="N5" s="10" t="s">
@@ -31427,46 +31213,46 @@
       <c r="Q5" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="R5" s="62"/>
-      <c r="S5" s="63" t="b">
+      <c r="R5" s="58"/>
+      <c r="S5" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
-      <c r="V5" s="63" t="b">
+      <c r="V5" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W5" s="63" t="b">
+      <c r="W5" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X5" s="59" t="n">
+      <c r="X5" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" s="66" t="s">
+      <c r="Y5" s="60" t="s">
         <v>287</v>
       </c>
-      <c r="Z5" s="59" t="n">
+      <c r="Z5" s="55" t="n">
         <v>20</v>
       </c>
       <c r="AA5" s="14"/>
-      <c r="AB5" s="66" t="s">
+      <c r="AB5" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="AC5" s="59" t="n">
+      <c r="AC5" s="55" t="n">
         <v>40</v>
       </c>
       <c r="AD5" s="14"/>
-      <c r="AE5" s="64" t="s">
+      <c r="AE5" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="AF5" s="59" t="n">
+      <c r="AF5" s="55" t="n">
         <v>60</v>
       </c>
       <c r="AG5" s="14"/>
-      <c r="AH5" s="64"/>
+      <c r="AH5" s="9"/>
       <c r="AI5" s="14"/>
       <c r="AJ5" s="14"/>
       <c r="AK5" s="14"/>
@@ -31532,7 +31318,7 @@
       <c r="D6" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="E6" s="59" t="n">
+      <c r="E6" s="55" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="14"/>
@@ -31542,13 +31328,13 @@
       <c r="J6" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="K6" s="59" t="n">
+      <c r="K6" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="L6" s="65" t="s">
+      <c r="L6" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="M6" s="61" t="s">
+      <c r="M6" s="57" t="s">
         <v>292</v>
       </c>
       <c r="N6" s="10" t="s">
@@ -31559,29 +31345,29 @@
       <c r="Q6" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="R6" s="62"/>
-      <c r="S6" s="63" t="b">
+      <c r="R6" s="58"/>
+      <c r="S6" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
-      <c r="V6" s="63" t="b">
+      <c r="V6" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="W6" s="63" t="b">
+      <c r="W6" s="58" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="X6" s="59" t="n">
+      <c r="X6" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="66"/>
-      <c r="Z6" s="59"/>
+      <c r="Y6" s="60"/>
+      <c r="Z6" s="55"/>
       <c r="AA6" s="14"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="59"/>
+      <c r="AB6" s="60"/>
+      <c r="AC6" s="55"/>
       <c r="AD6" s="14"/>
       <c r="AE6" s="14"/>
       <c r="AF6" s="14"/>
@@ -31704,87 +31490,87 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="297" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="67" t="s">
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="61" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="68" t="s">
+      <c r="E2" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="63" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="70" t="n">
+      <c r="B3" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="65" t="s">
         <v>296</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="F3" s="72"/>
+      <c r="F3" s="66"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="70" t="n">
+      <c r="B4" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="65" t="s">
         <v>296</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="65" t="s">
         <v>298</v>
       </c>
     </row>
@@ -31813,95 +31599,94 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="359.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="D1" s="73" t="s">
+      <c r="D1" s="67" t="s">
         <v>302</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="68" t="s">
         <v>303</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="E2" s="68" t="s">
         <v>304</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="F2" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="69" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="64" t="s">
         <v>165</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="D3" s="65" t="s">
         <v>296</v>
       </c>
-      <c r="E3" s="71" t="s">
+      <c r="E3" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="65" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="64" t="s">
         <v>171</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="65" t="s">
         <v>296</v>
       </c>
-      <c r="E4" s="71" t="s">
+      <c r="E4" s="65" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="65" t="s">
         <v>298</v>
       </c>
     </row>
